--- a/client/dist/Sorce/balanceML.xlsx
+++ b/client/dist/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 09.02.2025 14:55:12</t>
+    <t>Период: на 23.12.2025 16:15:14</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>

--- a/client/dist/Sorce/balanceML.xlsx
+++ b/client/dist/Sorce/balanceML.xlsx
@@ -19,7 +19,7 @@
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.12.2025 16:15:14</t>
+    <t>Период: на 23.02.2026 11:15:13</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
